--- a/AAII_Financials/Quarterly/ACIU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ACIU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="92">
   <si>
     <t>ACIU</t>
   </si>
@@ -656,215 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E8" s="3">
         <v>400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>30200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>800</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L8" s="3">
         <v>17600</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
         <v>4400</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
       <c r="R8" s="3">
         <v>0</v>
       </c>
@@ -881,100 +885,103 @@
         <v>0</v>
       </c>
       <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
         <v>1000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>13300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>36400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>83000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>16500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E9" s="3">
         <v>13400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>21200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>17400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>17100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>19100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>17400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15200</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1050,47 +1057,50 @@
       <c r="AN9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E10" s="3">
         <v>-13000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-19500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-16900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-16200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>13000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-18300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-16800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-13600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-15300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-15200</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1166,8 +1176,11 @@
       <c r="AN10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1208,124 +1221,128 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E12" s="3">
         <v>13400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>21200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>18000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>17400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>17100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>19100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>16800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>17400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>13600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>15300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>15200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>17800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>16100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>17800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>17000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>22600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>16700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>14700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>14300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>17100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>16100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>12800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>16300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>16000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>12500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>13500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>12800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>13400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>12000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>10800</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>10300</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>8200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>6900</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>7600</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>7200</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,16 +1457,19 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
@@ -1478,8 +1498,8 @@
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1556,19 +1576,22 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>300</v>
+      </c>
+      <c r="E15" s="3">
         <v>400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>500</v>
-      </c>
-      <c r="F15" s="3">
-        <v>400</v>
       </c>
       <c r="G15" s="3">
         <v>400</v>
@@ -1583,7 +1606,7 @@
         <v>400</v>
       </c>
       <c r="K15" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="L15" s="3">
         <v>500</v>
@@ -1595,7 +1618,7 @@
         <v>500</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1645,8 +1668,8 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>5</v>
+      <c r="AF15" s="3">
+        <v>0</v>
       </c>
       <c r="AG15" s="3" t="s">
         <v>5</v>
@@ -1663,8 +1686,8 @@
       <c r="AK15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AL15" s="3">
-        <v>100</v>
+      <c r="AL15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AM15" s="3">
         <v>100</v>
@@ -1672,8 +1695,11 @@
       <c r="AN15" s="3">
         <v>100</v>
       </c>
+      <c r="AO15" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1737,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E17" s="3">
         <v>18600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>26000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>23000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>21800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>21600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>24100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>22200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>21800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>19000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>19300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>22000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>19500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>22500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>21200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>25600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>22400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>20000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>18500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>21900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>20700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>16900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>21100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>21600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>16800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>17300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>16500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>17500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>15000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>14000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>13100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>13300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>10800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>9000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>10200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>10900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-18200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-24400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-21900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-20500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-23300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-22200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-16900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-19000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-19300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-22000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-22500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-21200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-25600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-22400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-20000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-18500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-20900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-19500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-15600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-7800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-20400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>19600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-15700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>66500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-12600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-11900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-11600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-9700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-8200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-8100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-9400</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,240 +2018,247 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>5000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>600</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>5000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-4100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>4500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-18100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-26700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-21800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-18000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-25700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-20000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-16400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-18600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-18800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-21400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-14400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-21400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-20400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-23000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-16700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-19600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-17300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-20300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-19100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-15200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-20400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>20400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-17000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>72000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-15600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-13700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-11200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-11700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>4400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-8700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-12200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-9700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>-4900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2232,7 +2272,7 @@
         <v>100</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -2253,19 +2293,19 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="3">
         <v>100</v>
       </c>
       <c r="R22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S22" s="3">
         <v>200</v>
@@ -2277,7 +2317,7 @@
         <v>200</v>
       </c>
       <c r="V22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -2286,29 +2326,29 @@
         <v>0</v>
       </c>
       <c r="Y22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="3">
         <v>100</v>
       </c>
       <c r="AA22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB22" s="3">
         <v>200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>300</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
-      </c>
       <c r="AG22" s="3">
         <v>0</v>
       </c>
@@ -2316,141 +2356,147 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>100</v>
       </c>
-      <c r="AJ22" s="3">
-        <v>0</v>
-      </c>
       <c r="AK22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="3">
         <v>100</v>
       </c>
-      <c r="AL22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AN22" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO22" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-18100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-26600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-21500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-17400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-25300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-19800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-16600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-18800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-19200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-22100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-22200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-21200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-23900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-17600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-20400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-17900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-20900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-15700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-21200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>19800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>70300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-16200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-14000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-11400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-11900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-8800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-12400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-9800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2463,11 +2509,11 @@
       <c r="F24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>5</v>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>5</v>
@@ -2475,8 +2521,8 @@
       <c r="J24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -2565,8 +2611,11 @@
       <c r="AN24" s="3">
         <v>0</v>
       </c>
+      <c r="AO24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2730,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-18100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-26600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-21500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-25300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-19800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-16600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-18800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-19200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-22100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-22200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-21200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-23900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-17600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-20400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-17900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-20900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-15700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-21200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>19800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>70300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-16200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-14000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-11400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-11900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-8800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-12400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-9800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-4900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-18100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-26600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-21500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-25300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-19800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-16600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-18800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-19200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-22100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-22200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-21200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-23900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-17600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-20400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-17900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-20900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-15700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-21200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>19800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>70300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-16200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-14000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-11400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-11900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-8800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-12400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-9800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-4900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3087,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3145,8 +3206,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3325,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,240 +3444,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-5000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-600</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>4100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>1700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-4500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-18100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-26600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-21500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-25300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-19800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-16600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-18800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-19200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-22100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-22200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-21200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-23900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-17600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-20400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-17900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-20900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-15700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-21200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>19800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>70300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-16200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-14000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-11400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-11900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-8800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-12400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-9800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-4900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3801,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-18100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-26600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-21500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-25300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-19800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-16600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-18800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-19200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-22100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-22200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-21200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-23900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-17600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-20400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-17900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-20900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-15700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-21200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>19800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>70300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-16200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-14000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-11400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-11900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-8800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-12400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-9800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-4900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4089,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,214 +4132,218 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E41" s="3">
         <v>33800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>32300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>22600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>40000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>38400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>57400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>63200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>93200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>34900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>44700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>62900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>37200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>49800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>71400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>65100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>92500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>103400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>111700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>162000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>172500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>183200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>177000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>195700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>210700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>231300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>218900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>245700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>172300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>206500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>105400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>112600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>124900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>117700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>124700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>143000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>157600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>163200</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E42" s="3">
         <v>81500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>127500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>142200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>142600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>148500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>137500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>53000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>29200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>52500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>59200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>52600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>107200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>107400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>103000</v>
-      </c>
-      <c r="R42" s="3">
-        <v>130600</v>
       </c>
       <c r="S42" s="3">
         <v>130600</v>
       </c>
       <c r="T42" s="3">
+        <v>130600</v>
+      </c>
+      <c r="U42" s="3">
         <v>104900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>101900</v>
-      </c>
-      <c r="V42" s="3">
-        <v>69700</v>
       </c>
       <c r="W42" s="3">
         <v>69700</v>
       </c>
       <c r="X42" s="3">
+        <v>69700</v>
+      </c>
+      <c r="Y42" s="3">
         <v>72600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>84800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>101600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>103400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>98000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>85100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>88500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>33000</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG42" s="3" t="s">
         <v>5</v>
       </c>
@@ -4269,8 +4359,8 @@
       <c r="AK42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AL42" s="3">
-        <v>0</v>
+      <c r="AL42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AM42" s="3">
         <v>0</v>
@@ -4278,124 +4368,130 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E43" s="3">
         <v>900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>31100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>18200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1100</v>
-      </c>
-      <c r="N43" s="3">
-        <v>900</v>
       </c>
       <c r="O43" s="3">
         <v>900</v>
       </c>
       <c r="P43" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q43" s="3">
         <v>4700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1500</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4432,8 +4528,8 @@
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4510,240 +4606,249 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3">
         <v>800</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3">
         <v>800</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P45" s="3">
         <v>5500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2900</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>3700</v>
       </c>
       <c r="Z45" s="3">
         <v>3700</v>
       </c>
       <c r="AA45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AB45" s="3">
         <v>3000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1400</v>
-      </c>
-      <c r="AJ45" s="3">
-        <v>2000</v>
       </c>
       <c r="AK45" s="3">
         <v>2000</v>
       </c>
       <c r="AL45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AM45" s="3">
         <v>2400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1300</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>115600</v>
+      </c>
+      <c r="E46" s="3">
         <v>122000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>165700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>172100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>189800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>222100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>200900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>121800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>148600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>94200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>110800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>122400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>150900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>165100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>179200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>199300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>228100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>215800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>217500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>236400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>248500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>260000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>266400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>301800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>318700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>336800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>308900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>339500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>212500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>212800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>111700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>119500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>130100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>123300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>129300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>147400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>160400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>165400</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4780,8 +4885,8 @@
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O47" s="3">
-        <v>400</v>
+      <c r="O47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P47" s="3">
         <v>400</v>
@@ -4808,7 +4913,7 @@
         <v>400</v>
       </c>
       <c r="X47" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Y47" s="3">
         <v>300</v>
@@ -4832,7 +4937,7 @@
         <v>300</v>
       </c>
       <c r="AF47" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AG47" s="3">
         <v>200</v>
@@ -4841,7 +4946,7 @@
         <v>200</v>
       </c>
       <c r="AI47" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AJ47" s="3">
         <v>100</v>
@@ -4852,183 +4957,189 @@
       <c r="AL47" s="3">
         <v>100</v>
       </c>
-      <c r="AM47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN47" s="3">
+      <c r="AM47" s="3">
         <v>100</v>
       </c>
+      <c r="AN47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO47" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E48" s="3">
         <v>8200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8900</v>
-      </c>
-      <c r="H48" s="3">
-        <v>6900</v>
       </c>
       <c r="I48" s="3">
         <v>6900</v>
       </c>
       <c r="J48" s="3">
+        <v>6900</v>
+      </c>
+      <c r="K48" s="3">
         <v>7300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8000</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>8600</v>
       </c>
       <c r="R48" s="3">
         <v>8600</v>
       </c>
       <c r="S48" s="3">
+        <v>8600</v>
+      </c>
+      <c r="T48" s="3">
         <v>9000</v>
-      </c>
-      <c r="T48" s="3">
-        <v>8400</v>
       </c>
       <c r="U48" s="3">
         <v>8400</v>
       </c>
       <c r="V48" s="3">
+        <v>8400</v>
+      </c>
+      <c r="W48" s="3">
         <v>7600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>62400</v>
+      </c>
+      <c r="E49" s="3">
         <v>63600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>63400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>57000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>55600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>59700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>56100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>55900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>59900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>55100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>56300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>55200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>59400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>56400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>57000</v>
-      </c>
-      <c r="R49" s="3">
-        <v>56700</v>
       </c>
       <c r="S49" s="3">
         <v>56700</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>5</v>
+      <c r="T49" s="3">
+        <v>56700</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>5</v>
@@ -5045,8 +5156,8 @@
       <c r="Y49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
+      <c r="Z49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA49" s="3">
         <v>0</v>
@@ -5090,8 +5201,11 @@
       <c r="AN49" s="3">
         <v>0</v>
       </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5320,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,8 +5439,11 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5337,7 +5457,7 @@
         <v>700</v>
       </c>
       <c r="G52" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="H52" s="3">
         <v>500</v>
@@ -5349,7 +5469,7 @@
         <v>500</v>
       </c>
       <c r="K52" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="L52" s="3">
         <v>400</v>
@@ -5361,7 +5481,7 @@
         <v>400</v>
       </c>
       <c r="O52" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -5369,23 +5489,23 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>5</v>
+      <c r="R52" s="3">
+        <v>0</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V52" s="3">
         <v>100</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>5</v>
+      <c r="W52" s="3">
+        <v>100</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>5</v>
@@ -5402,8 +5522,8 @@
       <c r="AB52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC52" s="3">
-        <v>0</v>
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD52" s="3">
         <v>0</v>
@@ -5429,17 +5549,20 @@
       <c r="AK52" s="3">
         <v>0</v>
       </c>
-      <c r="AL52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM52" s="3">
+      <c r="AL52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN52" s="3">
         <v>100</v>
       </c>
-      <c r="AN52" s="3" t="s">
+      <c r="AO52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5677,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>186100</v>
+      </c>
+      <c r="E54" s="3">
         <v>194500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>239200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>238800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>254800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>289200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>264300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>185400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>217100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>156400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>174600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>185300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>219000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>229900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>245300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>265100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>294300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>224600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>226300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>244400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>256000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>266300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>272500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>308400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>325700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>343300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>315100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>346100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>216400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>216500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>115500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>123200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>132600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>126000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>131900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>149700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>161600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>166400</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5841,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,153 +5884,157 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E57" s="3">
         <v>2600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>200</v>
       </c>
-      <c r="AB57" s="3">
-        <v>0</v>
-      </c>
       <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="3">
         <v>200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>4200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1100</v>
-      </c>
-      <c r="H58" s="3">
-        <v>800</v>
       </c>
       <c r="I58" s="3">
         <v>800</v>
       </c>
       <c r="J58" s="3">
+        <v>800</v>
+      </c>
+      <c r="K58" s="3">
         <v>700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>800</v>
-      </c>
-      <c r="L58" s="3">
-        <v>600</v>
       </c>
       <c r="M58" s="3">
         <v>600</v>
@@ -5915,10 +6049,10 @@
         <v>600</v>
       </c>
       <c r="Q58" s="3">
+        <v>600</v>
+      </c>
+      <c r="R58" s="3">
         <v>700</v>
-      </c>
-      <c r="R58" s="3">
-        <v>600</v>
       </c>
       <c r="S58" s="3">
         <v>600</v>
@@ -5930,13 +6064,13 @@
         <v>600</v>
       </c>
       <c r="V58" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W58" s="3">
         <v>500</v>
       </c>
       <c r="X58" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="Y58" s="3">
         <v>800</v>
@@ -5945,23 +6079,23 @@
         <v>800</v>
       </c>
       <c r="AA58" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB58" s="3">
         <v>1200</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>800</v>
       </c>
       <c r="AC58" s="3">
         <v>800</v>
       </c>
       <c r="AD58" s="3">
+        <v>800</v>
+      </c>
+      <c r="AE58" s="3">
         <v>52500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>400</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG58" s="3" t="s">
         <v>5</v>
       </c>
@@ -5977,8 +6111,8 @@
       <c r="AK58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AL58" s="3">
-        <v>0</v>
+      <c r="AL58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AM58" s="3">
         <v>0</v>
@@ -5986,335 +6120,344 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>112300</v>
+      </c>
+      <c r="E59" s="3">
         <v>105900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>105300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>95800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>93900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>101800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>96300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>400</v>
-      </c>
-      <c r="M59" s="3">
-        <v>500</v>
       </c>
       <c r="N59" s="3">
         <v>500</v>
       </c>
       <c r="O59" s="3">
+        <v>500</v>
+      </c>
+      <c r="P59" s="3">
         <v>11800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>19600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>12200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>12500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>10700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>12600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>17700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>14400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>13100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>13700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>11900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>10500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>9500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>7600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>8700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>6900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>5000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>5200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>6100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>124100</v>
+      </c>
+      <c r="E60" s="3">
         <v>119400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>124400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>112300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>111300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>119600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>111900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>16100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>15200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>13500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>13400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>22500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>15700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>15000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>14400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>12900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>14200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>19100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>15300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>14100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>67100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>14400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>11100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>11600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>8800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>9800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>8300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>6000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>7900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>10300</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>11400</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4900</v>
-      </c>
-      <c r="H61" s="3">
-        <v>2800</v>
       </c>
       <c r="I61" s="3">
         <v>2800</v>
       </c>
       <c r="J61" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K61" s="3">
         <v>2900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2000</v>
-      </c>
-      <c r="AB61" s="3">
-        <v>1900</v>
       </c>
       <c r="AC61" s="3">
         <v>1900</v>
       </c>
       <c r="AD61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AE61" s="3">
         <v>2100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>200</v>
-      </c>
-      <c r="AF61" s="3">
-        <v>600</v>
       </c>
       <c r="AG61" s="3">
         <v>600</v>
       </c>
       <c r="AH61" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="AI61" s="3">
         <v>400</v>
@@ -6326,7 +6469,7 @@
         <v>400</v>
       </c>
       <c r="AL61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AM61" s="3">
         <v>0</v>
@@ -6334,8 +6477,11 @@
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6372,86 +6518,89 @@
       <c r="N62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P62" s="3">
         <v>3800</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
       <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
         <v>8200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>9300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>5500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>5300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>4200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>4100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>4000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>3900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6715,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6834,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +6953,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>142600</v>
+      </c>
+      <c r="E66" s="3">
         <v>137900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>145200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>131600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>130900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>135100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>127000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>26300</v>
-      </c>
-      <c r="L66" s="3">
-        <v>18900</v>
       </c>
       <c r="M66" s="3">
         <v>18900</v>
       </c>
       <c r="N66" s="3">
+        <v>18900</v>
+      </c>
+      <c r="O66" s="3">
         <v>17800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>20000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>17300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>15800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>24100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>33200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>26700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>23400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>22000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>24900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>24200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>22300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>24200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>29200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>25000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>24400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>78600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>20800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>17400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>17600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>14600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>15200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>12800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>10400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>12000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>14200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7117,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7234,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7353,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7472,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7591,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-557500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-553700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-511700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-436900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-406400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-413100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-394600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-368700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-375500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-339500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-330800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-306900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-311000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-271800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-260400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-246200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-226200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-200600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-179100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-159500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-142500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-119400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-96900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-88200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-82200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-60400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-78900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-63900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-134200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-111400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-96600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-85900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-72900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-77000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-68800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-58300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-48600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7829,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7948,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8067,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E76" s="3">
         <v>56600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>94000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>107200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>123900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>154100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>137400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>160400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>190800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>137400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>155700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>167600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>199100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>212600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>229500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>241000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>261100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>197900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>203000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>222400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>231100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>242000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>250100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>284200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>296600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>318300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>290700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>267500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>195600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>199100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>97900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>108600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>117400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>113200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>121400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>137800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>147400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8305,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-18100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-26600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-21500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-25300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-19800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-16600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-18800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-19200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-22100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-22200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-21200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-23900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-17600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-20400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-17900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-20900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-15700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-21200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>19800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>70300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-16200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-14000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-11400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-11900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-8800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-12400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-9800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-4900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,8 +8593,9 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8410,10 +8609,10 @@
         <v>600</v>
       </c>
       <c r="G83" s="3">
+        <v>600</v>
+      </c>
+      <c r="H83" s="3">
         <v>700</v>
-      </c>
-      <c r="H83" s="3">
-        <v>600</v>
       </c>
       <c r="I83" s="3">
         <v>600</v>
@@ -8422,25 +8621,25 @@
         <v>600</v>
       </c>
       <c r="K83" s="3">
+        <v>600</v>
+      </c>
+      <c r="L83" s="3">
         <v>700</v>
-      </c>
-      <c r="L83" s="3">
-        <v>600</v>
       </c>
       <c r="M83" s="3">
         <v>600</v>
       </c>
       <c r="N83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="O83" s="3">
         <v>700</v>
       </c>
       <c r="P83" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q83" s="3">
         <v>600</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>700</v>
       </c>
       <c r="R83" s="3">
         <v>700</v>
@@ -8452,7 +8651,7 @@
         <v>700</v>
       </c>
       <c r="U83" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="V83" s="3">
         <v>600</v>
@@ -8461,7 +8660,7 @@
         <v>600</v>
       </c>
       <c r="X83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="Y83" s="3">
         <v>500</v>
@@ -8476,13 +8675,13 @@
         <v>500</v>
       </c>
       <c r="AC83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AD83" s="3">
         <v>400</v>
       </c>
       <c r="AE83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AF83" s="3">
         <v>300</v>
@@ -8491,7 +8690,7 @@
         <v>300</v>
       </c>
       <c r="AH83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AI83" s="3">
         <v>200</v>
@@ -8500,7 +8699,7 @@
         <v>200</v>
       </c>
       <c r="AK83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AL83" s="3">
         <v>100</v>
@@ -8511,8 +8710,11 @@
       <c r="AN83" s="3">
         <v>100</v>
       </c>
+      <c r="AO83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8829,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8948,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9067,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9186,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9305,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3">
         <v>-20800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-19600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-21300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-16700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>81300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-19200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-15800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-18400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-20500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-22000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-26000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-20100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-16000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-17200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-18600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-20800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-16200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-14800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-10400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-13900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>18500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>73000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-12900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-12300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-7300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-13700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>6400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-7600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-9100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-12300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-7200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,124 +9469,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-200</v>
       </c>
       <c r="N91" s="3">
         <v>-200</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-500</v>
       </c>
       <c r="R91" s="3">
         <v>-500</v>
       </c>
       <c r="S91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="T91" s="3">
         <v>-700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI91" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-600</v>
-      </c>
-      <c r="AM91" s="3">
-        <v>-300</v>
       </c>
       <c r="AN91" s="3">
         <v>-300</v>
       </c>
+      <c r="AO91" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9705,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +9824,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3">
         <v>20200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>30000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>3400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-84400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-26100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>27600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>5200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>46900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>5800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>27700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-24400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-32900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>4500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>15300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>9600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-11400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-55900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-33400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI94" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="3">
         <v>-300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-700</v>
-      </c>
-      <c r="AM94" s="3">
-        <v>-300</v>
       </c>
       <c r="AN94" s="3">
         <v>-300</v>
       </c>
+      <c r="AO94" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,8 +9988,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9793,8 +10027,8 @@
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9871,8 +10105,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10224,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10343,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,13 +10462,16 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>-300</v>
+      <c r="D100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E100" s="3">
         <v>-300</v>
@@ -10234,28 +10480,28 @@
         <v>-300</v>
       </c>
       <c r="G100" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="H100" s="3">
         <v>-200</v>
       </c>
       <c r="I100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>48700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2100</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-200</v>
       </c>
       <c r="O100" s="3">
         <v>-200</v>
@@ -10267,58 +10513,58 @@
         <v>-200</v>
       </c>
       <c r="R100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S100" s="3">
         <v>-1000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>32300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4800</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>8300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-400</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>55600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>113800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>100</v>
       </c>
-      <c r="AH100" s="3">
-        <v>0</v>
-      </c>
       <c r="AI100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AJ100" s="3">
         <v>100</v>
@@ -10327,244 +10573,253 @@
         <v>100</v>
       </c>
       <c r="AL100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN100" s="3">
         <v>-2600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>70500</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-3200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>700</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-200</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-500</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>4400</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-18500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-22700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-23800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>55300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-19500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>28300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-15200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-20900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-27400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-12800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-11700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-50400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-10500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-16800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-11500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-20500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>7300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-17500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>72600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-47000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>100000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-7200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-15100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>7200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-7000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-14000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-14600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-5600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>77900</v>
       </c>
     </row>
